--- a/EA流程架构项目/_VNW引用原件/L4流程_Skill封装可行性评估_确认最终版_v2.xlsx
+++ b/EA流程架构项目/_VNW引用原件/L4流程_Skill封装可行性评估_确认最终版_v2.xlsx
@@ -584,9 +584,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23">
         <f>== 2026-07-09 同步更新：与自动化Tier两阶段复核方法论的关系说明 ===</f>
@@ -621,9 +619,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -996,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N369"/>
+  <dimension ref="A1:N393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1148,8 +1144,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1212,8 +1206,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1276,7 +1268,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>是</t>
@@ -1344,8 +1335,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1408,8 +1397,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1472,8 +1459,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1536,8 +1521,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1600,8 +1583,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1732,8 +1713,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1864,8 +1843,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1928,8 +1905,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1997,7 +1972,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2060,8 +2034,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2124,8 +2096,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2188,8 +2158,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2252,8 +2220,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2316,8 +2282,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2380,8 +2344,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2444,8 +2406,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2508,8 +2468,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2572,8 +2530,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2636,8 +2592,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2768,8 +2722,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2832,8 +2784,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2896,8 +2846,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2960,8 +2908,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3024,8 +2970,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3088,8 +3032,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3220,8 +3162,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3284,8 +3224,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3348,8 +3286,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3412,8 +3348,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3476,8 +3410,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3540,8 +3472,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3604,8 +3534,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3668,8 +3596,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3732,8 +3658,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3796,8 +3720,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3860,8 +3782,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3924,8 +3844,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4124,8 +4042,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4188,8 +4104,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4252,8 +4166,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4316,8 +4228,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4380,8 +4290,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4444,8 +4352,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4508,8 +4414,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4572,8 +4476,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4636,8 +4538,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4700,8 +4600,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4764,8 +4662,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4828,8 +4724,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4892,8 +4786,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4956,8 +4848,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5020,8 +4910,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5084,8 +4972,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5148,8 +5034,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5212,8 +5096,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5276,8 +5158,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5340,8 +5220,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5404,8 +5282,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5468,8 +5344,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5537,7 +5411,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5600,8 +5473,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5664,8 +5535,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5728,8 +5597,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5792,8 +5659,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5856,8 +5721,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5920,8 +5783,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5984,8 +5845,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6048,8 +5907,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6112,8 +5969,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6380,8 +6235,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6444,8 +6297,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6508,8 +6359,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6572,8 +6421,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6636,8 +6483,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6700,8 +6545,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6764,8 +6607,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6828,8 +6669,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6892,8 +6731,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6956,8 +6793,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7020,8 +6855,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7084,8 +6917,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7148,8 +6979,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7212,8 +7041,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -7344,7 +7171,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>是</t>
@@ -7412,8 +7238,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7476,8 +7300,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7540,8 +7362,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -7672,8 +7492,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7736,8 +7554,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7800,8 +7616,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7864,7 +7678,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>是</t>
@@ -7932,8 +7745,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7996,8 +7807,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8060,8 +7869,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8124,8 +7931,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8188,8 +7993,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8252,8 +8055,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8316,8 +8117,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8380,8 +8179,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8444,8 +8241,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8508,8 +8303,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8572,8 +8365,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8636,8 +8427,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8700,7 +8489,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>是</t>
@@ -8768,8 +8556,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -8900,8 +8686,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8964,8 +8748,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9028,8 +8810,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9092,8 +8872,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9156,8 +8934,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9220,8 +8996,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9284,8 +9058,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9348,8 +9120,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9412,8 +9182,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9476,8 +9244,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9540,8 +9306,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9604,8 +9368,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9668,8 +9430,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9732,8 +9492,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9796,8 +9554,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9860,8 +9616,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9924,8 +9678,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9988,8 +9740,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10052,8 +9802,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10116,8 +9864,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10180,8 +9926,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10244,8 +9988,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10308,8 +10050,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10372,8 +10112,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10436,8 +10174,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10500,8 +10236,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10564,8 +10298,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10628,8 +10360,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10692,8 +10422,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10761,7 +10489,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10824,8 +10551,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10888,8 +10613,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10952,8 +10675,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -11084,8 +10805,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11148,8 +10867,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11212,8 +10929,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11276,8 +10991,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11340,8 +11053,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -11472,8 +11183,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11536,7 +11245,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr">
         <is>
           <t>是</t>
@@ -11604,8 +11312,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11668,8 +11374,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11732,8 +11436,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11796,8 +11498,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11860,8 +11560,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11924,8 +11622,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11988,8 +11684,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12052,8 +11746,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12116,8 +11808,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12180,8 +11870,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12244,8 +11932,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12308,8 +11994,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12372,8 +12056,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12436,8 +12118,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12500,8 +12180,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12564,8 +12242,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12628,8 +12304,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12692,8 +12366,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12756,8 +12428,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12820,8 +12490,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12884,8 +12552,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12948,8 +12614,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13012,8 +12676,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13076,8 +12738,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13140,8 +12800,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13204,8 +12862,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13268,8 +12924,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13332,8 +12986,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13396,8 +13048,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13460,8 +13110,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13524,8 +13172,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13588,8 +13234,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13652,8 +13296,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13716,8 +13358,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13780,8 +13420,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13844,8 +13482,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13908,8 +13544,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13972,8 +13606,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14036,8 +13668,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14100,8 +13730,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14164,8 +13792,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14228,8 +13854,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14292,8 +13916,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14356,7 +13978,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr">
         <is>
           <t>是</t>
@@ -14424,8 +14045,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14488,8 +14107,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14552,8 +14169,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14616,8 +14231,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14680,8 +14293,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14744,8 +14355,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -14808,8 +14417,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -14872,8 +14479,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -14936,8 +14541,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15000,8 +14603,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15064,8 +14665,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15128,8 +14727,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15192,8 +14789,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15256,8 +14851,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -15320,8 +14913,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -15384,8 +14975,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -15448,8 +15037,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -15512,8 +15099,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -15576,8 +15161,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15640,8 +15223,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -15704,8 +15285,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -15768,8 +15347,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -15832,7 +15409,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr">
         <is>
           <t>是</t>
@@ -15900,8 +15476,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15964,8 +15538,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16028,8 +15600,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16092,8 +15662,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16156,8 +15724,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -16220,8 +15786,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -16284,8 +15848,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -16348,8 +15910,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -16412,8 +15972,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -16476,8 +16034,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16540,8 +16096,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -16604,8 +16158,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -16736,8 +16288,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -16800,8 +16350,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16864,8 +16412,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -16928,8 +16474,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16992,8 +16536,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -17056,8 +16598,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17120,8 +16660,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -17184,8 +16722,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -17248,8 +16784,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr"/>
-      <c r="N252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -17312,8 +16846,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr"/>
-      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -17376,8 +16908,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17440,8 +16970,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -17504,8 +17032,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -17568,8 +17094,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr"/>
-      <c r="N257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -17632,8 +17156,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -17696,8 +17218,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -17760,8 +17280,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -17824,8 +17342,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -17888,8 +17404,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr"/>
-      <c r="N262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -17952,8 +17466,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr"/>
-      <c r="N263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18016,8 +17528,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -18080,8 +17590,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -18144,8 +17652,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -18208,8 +17714,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -18272,8 +17776,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M268" t="inlineStr"/>
-      <c r="N268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -18336,8 +17838,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr"/>
-      <c r="N269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -18400,8 +17900,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -18464,8 +17962,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr"/>
-      <c r="N271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -18528,8 +18024,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr"/>
-      <c r="N272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -18592,8 +18086,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr"/>
-      <c r="N273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -18656,8 +18148,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr"/>
-      <c r="N274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -18720,8 +18210,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr"/>
-      <c r="N275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -18784,8 +18272,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr"/>
-      <c r="N276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -18848,8 +18334,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -18912,8 +18396,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M278" t="inlineStr"/>
-      <c r="N278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -18976,8 +18458,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -19040,8 +18520,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -19104,8 +18582,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr"/>
-      <c r="N281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -19168,8 +18644,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -19232,8 +18706,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M283" t="inlineStr"/>
-      <c r="N283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -19296,8 +18768,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -19365,7 +18835,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -19428,8 +18897,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M286" t="inlineStr"/>
-      <c r="N286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -19492,8 +18959,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr"/>
-      <c r="N287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -19556,8 +19021,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr"/>
-      <c r="N288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -19620,8 +19083,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr"/>
-      <c r="N289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -19684,8 +19145,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -19748,8 +19207,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M291" t="inlineStr"/>
-      <c r="N291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -19812,8 +19269,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M292" t="inlineStr"/>
-      <c r="N292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -19876,8 +19331,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M293" t="inlineStr"/>
-      <c r="N293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -20008,8 +19461,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -20072,8 +19523,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -20136,8 +19585,6 @@
           <t>Auto</t>
         </is>
       </c>
-      <c r="M297" t="inlineStr"/>
-      <c r="N297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -20200,8 +19647,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M298" t="inlineStr"/>
-      <c r="N298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -20264,8 +19709,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M299" t="inlineStr"/>
-      <c r="N299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -20328,8 +19771,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M300" t="inlineStr"/>
-      <c r="N300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -20392,8 +19833,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M301" t="inlineStr"/>
-      <c r="N301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -20456,8 +19895,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -20520,8 +19957,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -20584,8 +20019,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M304" t="inlineStr"/>
-      <c r="N304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -20648,8 +20081,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M305" t="inlineStr"/>
-      <c r="N305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -20712,7 +20143,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr">
         <is>
           <t>是</t>
@@ -20780,8 +20210,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -20844,8 +20272,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M308" t="inlineStr"/>
-      <c r="N308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -20908,8 +20334,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -20972,8 +20396,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M310" t="inlineStr"/>
-      <c r="N310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -21036,8 +20458,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M311" t="inlineStr"/>
-      <c r="N311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -21100,8 +20520,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M312" t="inlineStr"/>
-      <c r="N312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -21164,8 +20582,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M313" t="inlineStr"/>
-      <c r="N313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -21228,8 +20644,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr"/>
-      <c r="N314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -21292,8 +20706,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr"/>
-      <c r="N315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -21356,8 +20768,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr"/>
-      <c r="N316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -21420,8 +20830,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr"/>
-      <c r="N317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -21484,8 +20892,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr"/>
-      <c r="N318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -21548,8 +20954,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr"/>
-      <c r="N319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -21748,8 +21152,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr"/>
-      <c r="N322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -21812,8 +21214,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr"/>
-      <c r="N323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -21876,8 +21276,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr"/>
-      <c r="N324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -22008,8 +21406,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -22072,8 +21468,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -22136,8 +21530,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr"/>
-      <c r="N328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -22200,8 +21592,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr"/>
-      <c r="N329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -22264,8 +21654,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M330" t="inlineStr"/>
-      <c r="N330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -22396,8 +21784,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M332" t="inlineStr"/>
-      <c r="N332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -22460,8 +21846,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M333" t="inlineStr"/>
-      <c r="N333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -22524,8 +21908,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M334" t="inlineStr"/>
-      <c r="N334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -22588,8 +21970,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -22652,8 +22032,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M336" t="inlineStr"/>
-      <c r="N336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -22716,8 +22094,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -22780,8 +22156,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -22844,8 +22218,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M339" t="inlineStr"/>
-      <c r="N339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -22908,8 +22280,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M340" t="inlineStr"/>
-      <c r="N340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -22972,8 +22342,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M341" t="inlineStr"/>
-      <c r="N341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -23036,8 +22404,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M342" t="inlineStr"/>
-      <c r="N342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -23168,8 +22534,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M344" t="inlineStr"/>
-      <c r="N344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -23232,8 +22596,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M345" t="inlineStr"/>
-      <c r="N345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -23364,8 +22726,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M347" t="inlineStr"/>
-      <c r="N347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -23428,8 +22788,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M348" t="inlineStr"/>
-      <c r="N348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -23492,8 +22850,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M349" t="inlineStr"/>
-      <c r="N349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -23556,8 +22912,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M350" t="inlineStr"/>
-      <c r="N350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -23620,8 +22974,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M351" t="inlineStr"/>
-      <c r="N351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -23684,8 +23036,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M352" t="inlineStr"/>
-      <c r="N352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -23748,8 +23098,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M353" t="inlineStr"/>
-      <c r="N353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -23812,8 +23160,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M354" t="inlineStr"/>
-      <c r="N354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -23876,8 +23222,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M355" t="inlineStr"/>
-      <c r="N355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -23940,8 +23284,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M356" t="inlineStr"/>
-      <c r="N356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -24004,8 +23346,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M357" t="inlineStr"/>
-      <c r="N357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -24068,8 +23408,6 @@
           <t>Aug</t>
         </is>
       </c>
-      <c r="M358" t="inlineStr"/>
-      <c r="N358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -24132,8 +23470,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M359" t="inlineStr"/>
-      <c r="N359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -24196,8 +23532,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M360" t="inlineStr"/>
-      <c r="N360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -24260,8 +23594,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M361" t="inlineStr"/>
-      <c r="N361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -24324,8 +23656,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M362" t="inlineStr"/>
-      <c r="N362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -24388,8 +23718,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M363" t="inlineStr"/>
-      <c r="N363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -24452,8 +23780,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M364" t="inlineStr"/>
-      <c r="N364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -24516,8 +23842,6 @@
           <t>Human</t>
         </is>
       </c>
-      <c r="M365" t="inlineStr"/>
-      <c r="N365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -24580,8 +23904,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M366" t="inlineStr"/>
-      <c r="N366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -24644,8 +23966,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M367" t="inlineStr"/>
-      <c r="N367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -24708,8 +24028,6 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M368" t="inlineStr"/>
-      <c r="N368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -24772,8 +24090,654 @@
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="M369" t="inlineStr"/>
-      <c r="N369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>L3-ACTV</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>商考及活动执行（出行公司）</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>L4-ACTV-01</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>商考活动服务（服务需求提交）</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>《服务需求单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>L3-ACTV</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>商考及活动执行（出行公司）</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>L4-ACTV-02</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>商考活动服务（服务处理与执行）</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>《服务执行记录》</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>L3-ACTV</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>商考及活动执行（出行公司）</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>L4-ACTV-03</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>商考活动服务（服务确认与反馈）</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>《服务确认书》</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>L3-BRND</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>品牌营销服务执行（新动力）</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>L4-BRND-01</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>品牌营销服务（服务需求提交）</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>《服务需求单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>L3-BRND</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>品牌营销服务执行（新动力）</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>L4-BRND-02</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>品牌营销服务（服务处理与执行）</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>《服务执行记录》</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>L3-BRND</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>品牌营销服务执行（新动力）</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>L4-BRND-03</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>品牌营销服务（服务确认与反馈）</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>《服务确认书》</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>L3-COCH</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>教练陪跑服务执行（保了么）</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>L4-COCH-01</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>教练陪跑服务（服务需求提交）</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>《服务需求单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>L3-COCH</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>教练陪跑服务执行（保了么）</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>L4-COCH-02</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>教练陪跑服务（服务处理与执行）</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>《服务执行记录》</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>L3-COCH</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>教练陪跑服务执行（保了么）</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>L4-COCH-03</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>教练陪跑服务（服务确认与反馈）</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>《服务确认书》</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>L3-CONS</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>咨询服务执行（比域）</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>L4-CONS-01</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>咨询顾问服务（服务需求提交）</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>《服务需求单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>L3-CONS</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>咨询服务执行（比域）</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>L4-CONS-02</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>咨询顾问服务（服务处理与执行）</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>《服务执行记录》</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>L3-CONS</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>咨询服务执行（比域）</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>L4-CONS-03</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>咨询顾问服务（服务确认与反馈）</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>《服务确认书》</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>L3-IMED</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>移民教育服务执行（迪邦）</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>L4-IMED-01</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>移民教育服务（服务需求提交）</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>《服务需求单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>L3-IMED</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>移民教育服务执行（迪邦）</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>L4-IMED-02</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>移民教育服务（服务处理与执行）</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>《服务执行记录》</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>L3-IMED</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>移民教育服务执行（迪邦）</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>L4-IMED-03</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>移民教育服务（服务确认与反馈）</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>《服务确认书》</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>L3-STLM</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>结算服务执行（塞尔斯）</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>L4-STLM-01</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>结算支持服务（服务需求提交）</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>《服务需求单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>L3-STLM</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>结算服务执行（塞尔斯）</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>L4-STLM-02</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>结算支持服务（服务处理与执行）</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>《服务执行记录》</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>L3-STLM</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>结算服务执行（塞尔斯）</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>L4-STLM-03</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>结算支持服务（服务确认与反馈）</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>《服务确认书》</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>L3-TRNG</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>课程培训服务执行（新动力）</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>L4-TRNG-01</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>课程培训服务（服务需求提交）</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>《服务需求单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>L3-TRNG</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>课程培训服务执行（新动力）</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>L4-TRNG-02</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>课程培训服务（服务处理与执行）</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>《服务执行记录》</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>L3-TRNG</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>课程培训服务执行（新动力）</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>L4-TRNG-03</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>课程培训服务（服务确认与反馈）</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>《服务确认书》</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>L3-TRVL</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>机酒车服务执行（出行公司）</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>L4-TRVL-01</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>机酒车出行服务（服务需求提交）</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>《服务需求单》</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>L3-TRVL</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>机酒车服务执行（出行公司）</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>L4-TRVL-02</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>机酒车出行服务（服务处理与执行）</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>《服务执行记录》</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>L3-TRVL</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>机酒车服务执行（出行公司）</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>L4-TRVL-03</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>机酒车出行服务（服务确认与反馈）</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>《服务确认书》</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
